--- a/tests/fixtures/digest/DIG-003-atlas-2026-10-09.xlsx
+++ b/tests/fixtures/digest/DIG-003-atlas-2026-10-09.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="259">
   <si>
     <t xml:space="preserve">ATLAS · stato del rilascio al 09/10/2026</t>
   </si>
@@ -791,6 +791,15 @@
   </si>
   <si>
     <t xml:space="preserve">Per un dubbio su una riga, un commento sulla cella o una mail: rispondo per iscritto entro il giorno lavorativo successivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. La prossima settimana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In programma il 09/10, 5 ore: prosegue, chiusura prevista il 12/10; il 12/10, 2 ore: chiusura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dal 15/10 al 19/10, 12 ore</t>
   </si>
 </sst>
 </file>
@@ -1646,385 +1655,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Ottimale per consegnare il 13/10</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Riepilogo!C31</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Ottimale per consegnare il 13/10</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:explosion val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2a78d6"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="ffffff"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="1baf7a"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="ffffff"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="eda100"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="ffffff"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4a3aa7"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="ffffff"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="eb6834"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="ffffff"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:separator>
-</c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:separator>
-</c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:separator>
-</c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:separator>
-</c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:separator>
-</c:separator>
-            </c:dLbl>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
-            <c:separator>
-</c:separator>
-            <c:showLeaderLines val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Riepilogo!$A$32:$A$36</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Architettura</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Sviluppo</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Deploy</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Fuori perimetro</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Fuori dal prodotto</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Riepilogo!$C$32:$C$36</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.652920962199313</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.206185567010309</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13745704467354</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.000104134124752681</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.0033322919920858</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -2052,36 +1682,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>130680</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>200160</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>163440</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="5850360" y="10563120"/>
-        <a:ext cx="4499640" cy="2699640"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2812,12 +2412,6 @@
       <c r="B31" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
@@ -2827,14 +2421,6 @@
         <f aca="false">'Ore lavorate'!$E$13</f>
         <v>0.103092783505155</v>
       </c>
-      <c r="C32" s="26" t="n">
-        <f aca="false">IF(SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))=0,0,MIN(1,(SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))/MAX(1,NETWORKDAYS('Come leggerlo'!$B$4,'Come leggerlo'!$B$6)))/('Ore lavorate'!$D$6/NETWORKDAYS('Ore lavorate'!$B$6,'Ore lavorate'!$C$6)))*SUMPRODUCT((Attività!$C$12:$C$18="Architettura")*((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))/SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13)))</f>
-        <v>0.652920962199313</v>
-      </c>
-      <c r="D32" s="27" t="n">
-        <f aca="false">C32-B32</f>
-        <v>0.549828178694158</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
@@ -2844,14 +2430,6 @@
         <f aca="false">'Ore lavorate'!$F$13</f>
         <v>0.185567010309278</v>
       </c>
-      <c r="C33" s="26" t="n">
-        <f aca="false">IF(SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))=0,0,MIN(1,(SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))/MAX(1,NETWORKDAYS('Come leggerlo'!$B$4,'Come leggerlo'!$B$6)))/('Ore lavorate'!$D$6/NETWORKDAYS('Ore lavorate'!$B$6,'Ore lavorate'!$C$6)))*SUMPRODUCT((Attività!$C$12:$C$18="Sviluppo")*((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))/SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13)))</f>
-        <v>0.206185567010309</v>
-      </c>
-      <c r="D33" s="27" t="n">
-        <f aca="false">C33-B33</f>
-        <v>0.0206185567010309</v>
-      </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
@@ -2861,14 +2439,6 @@
         <f aca="false">'Ore lavorate'!$G$13</f>
         <v>0.0309278350515464</v>
       </c>
-      <c r="C34" s="26" t="n">
-        <f aca="false">IF(SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))=0,0,MIN(1,(SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))/MAX(1,NETWORKDAYS('Come leggerlo'!$B$4,'Come leggerlo'!$B$6)))/('Ore lavorate'!$D$6/NETWORKDAYS('Ore lavorate'!$B$6,'Ore lavorate'!$C$6)))*SUMPRODUCT((Attività!$C$12:$C$18="Deploy")*((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))/SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13)))</f>
-        <v>0.13745704467354</v>
-      </c>
-      <c r="D34" s="27" t="n">
-        <f aca="false">C34-B34</f>
-        <v>0.106529209621993</v>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
@@ -2878,14 +2448,6 @@
         <f aca="false">'Ore lavorate'!$H$13</f>
         <v>0.0206185567010309</v>
       </c>
-      <c r="C35" s="26" t="n">
-        <f aca="false">IF(('Ore lavorate'!$H$13+'Ore lavorate'!$I$13)=0,0,(1-MIN(1,(SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))/MAX(1,NETWORKDAYS('Come leggerlo'!$B$4,'Come leggerlo'!$B$6)))/('Ore lavorate'!$D$6/NETWORKDAYS('Ore lavorate'!$B$6,'Ore lavorate'!$C$6))))*'Ore lavorate'!$H$13/('Ore lavorate'!$H$13+'Ore lavorate'!$I$13))</f>
-        <v>0.000104134124752681</v>
-      </c>
-      <c r="D35" s="27" t="n">
-        <f aca="false">C35-B35</f>
-        <v>-0.0205144225762782</v>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
@@ -2895,14 +2457,6 @@
         <f aca="false">'Ore lavorate'!$I$13</f>
         <v>0.65979381443299</v>
       </c>
-      <c r="C36" s="26" t="n">
-        <f aca="false">IF(('Ore lavorate'!$H$13+'Ore lavorate'!$I$13)=0,0,(1-MIN(1,(SUMPRODUCT(((Attività!$E$12:$E$18="S")*1+(Attività!$E$12:$E$18="M")*3+(Attività!$E$12:$E$18="L")*6+(Attività!$E$12:$E$18="XL")*13))/MAX(1,NETWORKDAYS('Come leggerlo'!$B$4,'Come leggerlo'!$B$6)))/('Ore lavorate'!$D$6/NETWORKDAYS('Ore lavorate'!$B$6,'Ore lavorate'!$C$6))))*'Ore lavorate'!$I$13/('Ore lavorate'!$H$13+'Ore lavorate'!$I$13))</f>
-        <v>0.0033322919920858</v>
-      </c>
-      <c r="D36" s="27" t="n">
-        <f aca="false">C36-B36</f>
-        <v>-0.656461522440904</v>
-      </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
@@ -2912,11 +2466,6 @@
         <f aca="false">SUM(B32:B36)</f>
         <v>1</v>
       </c>
-      <c r="C37" s="28" t="n">
-        <f aca="false">SUM(C32:C36)</f>
-        <v>1</v>
-      </c>
-      <c r="D37" s="29"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2942,11 +2491,6 @@
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>$F17="Scade oggi"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D32:D36">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>$D32&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2989,7 +2533,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3042,7 +2586,7 @@
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="16" t="s">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>79</v>
@@ -3050,16 +2594,16 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>76</v>
@@ -3069,18 +2613,18 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>53</v>
@@ -3096,10 +2640,10 @@
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="16" t="s">
-        <v>84</v>
+        <v>258</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
